--- a/data/美团.xlsx
+++ b/data/美团.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2517,23 +2517,21 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
+      <c r="A88" t="n">
+        <v>934</v>
       </c>
       <c r="B88" s="1" t="n">
-        <v>46271.14371527778</v>
+        <v>46274.77847222222</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>46271.14461805556</v>
+        <v>46274.78534722222</v>
       </c>
       <c r="D88" t="n">
-        <v>1.3</v>
+        <v>9.9</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率22，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -2543,23 +2541,21 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
+      <c r="A89" t="n">
+        <v>934</v>
       </c>
       <c r="B89" s="1" t="n">
-        <v>46272.27924768518</v>
+        <v>46275.29961805556</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>46272.28622685185</v>
+        <v>46275.30657407407</v>
       </c>
       <c r="D89" t="n">
-        <v>10.05</v>
+        <v>10.02</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率27，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -2575,17 +2571,17 @@
         </is>
       </c>
       <c r="B90" s="1" t="n">
-        <v>46272.29309027778</v>
+        <v>46271.14371527778</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46272.3000462963</v>
+        <v>46271.14461805556</v>
       </c>
       <c r="D90" t="n">
-        <v>10.02</v>
+        <v>1.3</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率22，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -2601,17 +2597,17 @@
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46272.31395833333</v>
+        <v>46272.27924768518</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46272.32091435185</v>
+        <v>46272.28622685185</v>
       </c>
       <c r="D91" t="n">
-        <v>10.02</v>
+        <v>10.05</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率19，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -2627,17 +2623,17 @@
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46272.32903935185</v>
+        <v>46272.29309027778</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46272.33603009259</v>
+        <v>46272.3000462963</v>
       </c>
       <c r="D92" t="n">
-        <v>10.07</v>
+        <v>10.02</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -2653,17 +2649,17 @@
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46274.77847222222</v>
+        <v>46272.31395833333</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46274.78534722222</v>
+        <v>46272.32091435185</v>
       </c>
       <c r="D93" t="n">
-        <v>9.9</v>
+        <v>10.02</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率19，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -2679,20 +2675,98 @@
         </is>
       </c>
       <c r="B94" s="1" t="n">
+        <v>46272.32903935185</v>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>46272.33603009259</v>
+      </c>
+      <c r="D94" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="n">
+        <v>46274.77847222222</v>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>46274.78534722222</v>
+      </c>
+      <c r="D95" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B96" s="1" t="n">
         <v>46275.29961805556</v>
       </c>
-      <c r="C94" s="1" t="n">
+      <c r="C96" s="1" t="n">
         <v>46275.30657407407</v>
       </c>
-      <c r="D94" t="n">
+      <c r="D96" t="n">
         <v>10.02</v>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E96" t="inlineStr">
         <is>
           <t>【美团】站点934：预定验价变价率27，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B97" s="1" t="n">
+        <v>46275.99393518519</v>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>46276.00092592592</v>
+      </c>
+      <c r="D97" t="n">
+        <v>10.07</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
         <is>
           <t>【美团】站点934恢复上线。</t>
         </is>

--- a/data/美团.xlsx
+++ b/data/美团.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2565,23 +2565,21 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
+      <c r="A90" t="n">
+        <v>934</v>
       </c>
       <c r="B90" s="1" t="n">
-        <v>46271.14371527778</v>
+        <v>46275.99393518519</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>46271.14461805556</v>
+        <v>46276.00092592592</v>
       </c>
       <c r="D90" t="n">
-        <v>1.3</v>
+        <v>10.07</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率22，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -2597,17 +2595,17 @@
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46272.27924768518</v>
+        <v>46271.14371527778</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46272.28622685185</v>
+        <v>46271.14461805556</v>
       </c>
       <c r="D91" t="n">
-        <v>10.05</v>
+        <v>1.3</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率22，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -2623,17 +2621,17 @@
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46272.29309027778</v>
+        <v>46272.27924768518</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46272.3000462963</v>
+        <v>46272.28622685185</v>
       </c>
       <c r="D92" t="n">
-        <v>10.02</v>
+        <v>10.05</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -2649,17 +2647,17 @@
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46272.31395833333</v>
+        <v>46272.29309027778</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46272.32091435185</v>
+        <v>46272.3000462963</v>
       </c>
       <c r="D93" t="n">
         <v>10.02</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率19，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -2675,17 +2673,17 @@
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>46272.32903935185</v>
+        <v>46272.31395833333</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46272.33603009259</v>
+        <v>46272.32091435185</v>
       </c>
       <c r="D94" t="n">
-        <v>10.07</v>
+        <v>10.02</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率19，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -2701,17 +2699,17 @@
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>46274.77847222222</v>
+        <v>46272.32903935185</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46274.78534722222</v>
+        <v>46272.33603009259</v>
       </c>
       <c r="D95" t="n">
-        <v>9.9</v>
+        <v>10.07</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -2727,17 +2725,17 @@
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>46275.29961805556</v>
+        <v>46274.77847222222</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46275.30657407407</v>
+        <v>46274.78534722222</v>
       </c>
       <c r="D96" t="n">
-        <v>10.02</v>
+        <v>9.9</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率27，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -2753,20 +2751,46 @@
         </is>
       </c>
       <c r="B97" s="1" t="n">
+        <v>46275.29961805556</v>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>46275.30657407407</v>
+      </c>
+      <c r="D97" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率27，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="n">
         <v>46275.99393518519</v>
       </c>
-      <c r="C97" s="1" t="n">
+      <c r="C98" s="1" t="n">
         <v>46276.00092592592</v>
       </c>
-      <c r="D97" t="n">
+      <c r="D98" t="n">
         <v>10.07</v>
       </c>
-      <c r="E97" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>【美团】站点934恢复上线。</t>
         </is>

--- a/data/美团.xlsx
+++ b/data/美团.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2595,17 +2595,17 @@
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46271.14371527778</v>
+        <v>46272.27924768518</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46271.14461805556</v>
+        <v>46272.28622685185</v>
       </c>
       <c r="D91" t="n">
-        <v>1.3</v>
+        <v>10.05</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率22，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -2621,17 +2621,17 @@
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46272.27924768518</v>
+        <v>46272.29309027778</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46272.28622685185</v>
+        <v>46272.3000462963</v>
       </c>
       <c r="D92" t="n">
-        <v>10.05</v>
+        <v>10.02</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -2647,17 +2647,17 @@
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46272.29309027778</v>
+        <v>46272.31395833333</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46272.3000462963</v>
+        <v>46272.32091435185</v>
       </c>
       <c r="D93" t="n">
         <v>10.02</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率19，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -2673,17 +2673,17 @@
         </is>
       </c>
       <c r="B94" s="1" t="n">
-        <v>46272.31395833333</v>
+        <v>46272.32903935185</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46272.32091435185</v>
+        <v>46272.33603009259</v>
       </c>
       <c r="D94" t="n">
-        <v>10.02</v>
+        <v>10.07</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率19，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -2699,17 +2699,17 @@
         </is>
       </c>
       <c r="B95" s="1" t="n">
-        <v>46272.32903935185</v>
+        <v>46274.77847222222</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>46272.33603009259</v>
+        <v>46274.78534722222</v>
       </c>
       <c r="D95" t="n">
-        <v>10.07</v>
+        <v>9.9</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -2725,17 +2725,17 @@
         </is>
       </c>
       <c r="B96" s="1" t="n">
-        <v>46274.77847222222</v>
+        <v>46275.29961805556</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>46274.78534722222</v>
+        <v>46275.30657407407</v>
       </c>
       <c r="D96" t="n">
-        <v>9.9</v>
+        <v>10.02</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率27，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -2751,46 +2751,20 @@
         </is>
       </c>
       <c r="B97" s="1" t="n">
-        <v>46275.29961805556</v>
+        <v>46275.99393518519</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>46275.30657407407</v>
+        <v>46276.00092592592</v>
       </c>
       <c r="D97" t="n">
-        <v>10.02</v>
+        <v>10.07</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率27，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B98" s="1" t="n">
-        <v>46275.99393518519</v>
-      </c>
-      <c r="C98" s="1" t="n">
-        <v>46276.00092592592</v>
-      </c>
-      <c r="D98" t="n">
-        <v>10.07</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
         <is>
           <t>【美团】站点934恢复上线。</t>
         </is>

--- a/data/美团.xlsx
+++ b/data/美团.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2595,17 +2595,17 @@
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46272.27924768518</v>
+        <v>46274.77847222222</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46272.28622685185</v>
+        <v>46274.78534722222</v>
       </c>
       <c r="D91" t="n">
-        <v>10.05</v>
+        <v>9.9</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -2621,17 +2621,17 @@
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46272.29309027778</v>
+        <v>46275.29961805556</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46272.3000462963</v>
+        <v>46275.30657407407</v>
       </c>
       <c r="D92" t="n">
         <v>10.02</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率27，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -2647,124 +2647,20 @@
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46272.31395833333</v>
+        <v>46275.99393518519</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46272.32091435185</v>
+        <v>46276.00092592592</v>
       </c>
       <c r="D93" t="n">
-        <v>10.02</v>
+        <v>10.07</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率19，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B94" s="1" t="n">
-        <v>46272.32903935185</v>
-      </c>
-      <c r="C94" s="1" t="n">
-        <v>46272.33603009259</v>
-      </c>
-      <c r="D94" t="n">
-        <v>10.07</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B95" s="1" t="n">
-        <v>46274.77847222222</v>
-      </c>
-      <c r="C95" s="1" t="n">
-        <v>46274.78534722222</v>
-      </c>
-      <c r="D95" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B96" s="1" t="n">
-        <v>46275.29961805556</v>
-      </c>
-      <c r="C96" s="1" t="n">
-        <v>46275.30657407407</v>
-      </c>
-      <c r="D96" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率27，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B97" s="1" t="n">
-        <v>46275.99393518519</v>
-      </c>
-      <c r="C97" s="1" t="n">
-        <v>46276.00092592592</v>
-      </c>
-      <c r="D97" t="n">
-        <v>10.07</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
         <is>
           <t>【美团】站点934恢复上线。</t>
         </is>

--- a/data/美团.xlsx
+++ b/data/美团.xlsx
@@ -2595,13 +2595,13 @@
         </is>
       </c>
       <c r="B91" s="1" t="n">
-        <v>46274.77847222222</v>
+        <v>46282.45922453704</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>46274.78534722222</v>
+        <v>46282.46618055556</v>
       </c>
       <c r="D91" t="n">
-        <v>9.9</v>
+        <v>10.02</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -2621,17 +2621,17 @@
         </is>
       </c>
       <c r="B92" s="1" t="n">
-        <v>46275.29961805556</v>
+        <v>46282.473125</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>46275.30657407407</v>
+        <v>46282.4799537037</v>
       </c>
       <c r="D92" t="n">
-        <v>10.02</v>
+        <v>9.83</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率27，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -2647,17 +2647,17 @@
         </is>
       </c>
       <c r="B93" s="1" t="n">
-        <v>46275.99393518519</v>
+        <v>46282.97300925926</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>46276.00092592592</v>
+        <v>46282.97993055556</v>
       </c>
       <c r="D93" t="n">
-        <v>10.07</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">

--- a/data/美团.xlsx
+++ b/data/美团.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2589,10 +2589,8 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
+      <c r="A91" t="n">
+        <v>934</v>
       </c>
       <c r="B91" s="1" t="n">
         <v>46282.45922453704</v>
@@ -2615,10 +2613,8 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
+      <c r="A92" t="n">
+        <v>934</v>
       </c>
       <c r="B92" s="1" t="n">
         <v>46282.473125</v>
@@ -2641,10 +2637,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
+      <c r="A93" t="n">
+        <v>934</v>
       </c>
       <c r="B93" s="1" t="n">
         <v>46282.97300925926</v>
@@ -2661,6 +2655,84 @@
         </is>
       </c>
       <c r="F93" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B94" s="1" t="n">
+        <v>46282.45922453704</v>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>46282.46618055556</v>
+      </c>
+      <c r="D94" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B95" s="1" t="n">
+        <v>46282.473125</v>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>46282.4799537037</v>
+      </c>
+      <c r="D95" t="n">
+        <v>9.83</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B96" s="1" t="n">
+        <v>46282.97300925926</v>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>46282.97993055556</v>
+      </c>
+      <c r="D96" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
         <is>
           <t>【美团】站点934恢复上线。</t>
         </is>

--- a/data/美团.xlsx
+++ b/data/美团.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2738,6 +2738,188 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B97" s="1" t="n">
+        <v>46286.48706018519</v>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>46286.49402777778</v>
+      </c>
+      <c r="D97" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率23，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B98" s="1" t="n">
+        <v>46286.50042824074</v>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>46286.50737268518</v>
+      </c>
+      <c r="D98" t="n">
+        <v>10</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率31，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>46286.5983912037</v>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>46286.60533564815</v>
+      </c>
+      <c r="D99" t="n">
+        <v>10</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>46287.11172453704</v>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>46287.11868055556</v>
+      </c>
+      <c r="D100" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率26，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B101" s="1" t="n">
+        <v>46287.12581018519</v>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>46287.13274305555</v>
+      </c>
+      <c r="D101" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率28，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>46287.30594907407</v>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>46287.31291666667</v>
+      </c>
+      <c r="D102" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B103" s="1" t="n">
+        <v>46287.32052083333</v>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>46287.32746527778</v>
+      </c>
+      <c r="D103" t="n">
+        <v>10</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/美团.xlsx
+++ b/data/美团.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2661,179 +2661,165 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
+      <c r="A94" t="n">
+        <v>934</v>
       </c>
       <c r="B94" s="1" t="n">
-        <v>46282.45922453704</v>
+        <v>46286.48706018519</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>46282.46618055556</v>
+        <v>46286.49402777778</v>
       </c>
       <c r="D94" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率23，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>934</v>
+      </c>
+      <c r="B95" s="1" t="n">
+        <v>46286.50042824074</v>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>46286.50737268518</v>
+      </c>
+      <c r="D95" t="n">
+        <v>10</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率31，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>934</v>
+      </c>
+      <c r="B96" s="1" t="n">
+        <v>46286.5983912037</v>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>46286.60533564815</v>
+      </c>
+      <c r="D96" t="n">
+        <v>10</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>934</v>
+      </c>
+      <c r="B97" s="1" t="n">
+        <v>46287.11172453704</v>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>46287.11868055556</v>
+      </c>
+      <c r="D97" t="n">
         <v>10.02</v>
       </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B95" s="1" t="n">
-        <v>46282.473125</v>
-      </c>
-      <c r="C95" s="1" t="n">
-        <v>46282.4799537037</v>
-      </c>
-      <c r="D95" t="n">
-        <v>9.83</v>
-      </c>
-      <c r="E95" t="inlineStr">
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率26，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>934</v>
+      </c>
+      <c r="B98" s="1" t="n">
+        <v>46287.12581018519</v>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>46287.13274305555</v>
+      </c>
+      <c r="D98" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率28，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>934</v>
+      </c>
+      <c r="B99" s="1" t="n">
+        <v>46287.30594907407</v>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>46287.31291666667</v>
+      </c>
+      <c r="D99" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="E99" t="inlineStr">
         <is>
           <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B96" s="1" t="n">
-        <v>46282.97300925926</v>
-      </c>
-      <c r="C96" s="1" t="n">
-        <v>46282.97993055556</v>
-      </c>
-      <c r="D96" t="n">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B97" s="1" t="n">
-        <v>46286.48706018519</v>
-      </c>
-      <c r="C97" s="1" t="n">
-        <v>46286.49402777778</v>
-      </c>
-      <c r="D97" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率23，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B98" s="1" t="n">
-        <v>46286.50042824074</v>
-      </c>
-      <c r="C98" s="1" t="n">
-        <v>46286.50737268518</v>
-      </c>
-      <c r="D98" t="n">
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>934</v>
+      </c>
+      <c r="B100" s="1" t="n">
+        <v>46287.32052083333</v>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>46287.32746527778</v>
+      </c>
+      <c r="D100" t="n">
         <v>10</v>
       </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率31，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B99" s="1" t="n">
-        <v>46286.5983912037</v>
-      </c>
-      <c r="C99" s="1" t="n">
-        <v>46286.60533564815</v>
-      </c>
-      <c r="D99" t="n">
-        <v>10</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B100" s="1" t="n">
-        <v>46287.11172453704</v>
-      </c>
-      <c r="C100" s="1" t="n">
-        <v>46287.11868055556</v>
-      </c>
-      <c r="D100" t="n">
-        <v>10.02</v>
-      </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率26，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -2849,17 +2835,17 @@
         </is>
       </c>
       <c r="B101" s="1" t="n">
-        <v>46287.12581018519</v>
+        <v>46282.97300925926</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46287.13274305555</v>
+        <v>46282.97993055556</v>
       </c>
       <c r="D101" t="n">
-        <v>9.98</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率28，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -2875,17 +2861,17 @@
         </is>
       </c>
       <c r="B102" s="1" t="n">
-        <v>46287.30594907407</v>
+        <v>46286.48706018519</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>46287.31291666667</v>
+        <v>46286.49402777778</v>
       </c>
       <c r="D102" t="n">
         <v>10.03</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率23，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -2901,20 +2887,332 @@
         </is>
       </c>
       <c r="B103" s="1" t="n">
-        <v>46287.32052083333</v>
+        <v>46286.50042824074</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>46287.32746527778</v>
+        <v>46286.50737268518</v>
       </c>
       <c r="D103" t="n">
         <v>10</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
+          <t>【美团】站点934：预定验价变价率31，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B104" s="1" t="n">
+        <v>46286.5983912037</v>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>46286.60533564815</v>
+      </c>
+      <c r="D104" t="n">
+        <v>10</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>46287.11172453704</v>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>46287.11868055556</v>
+      </c>
+      <c r="D105" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率26，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>46287.12581018519</v>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>46287.13274305555</v>
+      </c>
+      <c r="D106" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率28，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>46287.30594907407</v>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>46287.31291666667</v>
+      </c>
+      <c r="D107" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B108" s="1" t="n">
+        <v>46287.32052083333</v>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>46287.32746527778</v>
+      </c>
+      <c r="D108" t="n">
+        <v>10</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
           <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B109" s="1" t="n">
+        <v>46287.38972222222</v>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>46287.39673611111</v>
+      </c>
+      <c r="D109" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率27，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>46287.40336805556</v>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>46287.41027777778</v>
+      </c>
+      <c r="D110" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B111" s="1" t="n">
+        <v>46287.41793981481</v>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>46287.42490740741</v>
+      </c>
+      <c r="D111" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率21，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B112" s="1" t="n">
+        <v>46289.11177083333</v>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>46289.11864583333</v>
+      </c>
+      <c r="D112" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>46289.1255787037</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46289.1325</v>
+      </c>
+      <c r="D113" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率21，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B114" s="1" t="n">
+        <v>46289.29210648148</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46289.2990625</v>
+      </c>
+      <c r="D114" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B115" s="1" t="n">
+        <v>46289.30592592592</v>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>46289.31285879629</v>
+      </c>
+      <c r="D115" t="n">
+        <v>9.98</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
         <is>
           <t>【美团】站点934恢复上线。</t>
         </is>

--- a/data/美团.xlsx
+++ b/data/美团.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2829,179 +2829,165 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
+      <c r="A101" t="n">
+        <v>934</v>
       </c>
       <c r="B101" s="1" t="n">
-        <v>46282.97300925926</v>
+        <v>46287.38972222222</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>46282.97993055556</v>
+        <v>46287.39673611111</v>
       </c>
       <c r="D101" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率27，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>934</v>
+      </c>
+      <c r="B102" s="1" t="n">
+        <v>46287.40336805556</v>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>46287.41027777778</v>
+      </c>
+      <c r="D102" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>934</v>
+      </c>
+      <c r="B103" s="1" t="n">
+        <v>46287.41793981481</v>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>46287.42490740741</v>
+      </c>
+      <c r="D103" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率21，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>934</v>
+      </c>
+      <c r="B104" s="1" t="n">
+        <v>46289.11177083333</v>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>46289.11864583333</v>
+      </c>
+      <c r="D104" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>934</v>
+      </c>
+      <c r="B105" s="1" t="n">
+        <v>46289.1255787037</v>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>46289.1325</v>
+      </c>
+      <c r="D105" t="n">
         <v>9.970000000000001</v>
       </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B102" s="1" t="n">
-        <v>46286.48706018519</v>
-      </c>
-      <c r="C102" s="1" t="n">
-        <v>46286.49402777778</v>
-      </c>
-      <c r="D102" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率23，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B103" s="1" t="n">
-        <v>46286.50042824074</v>
-      </c>
-      <c r="C103" s="1" t="n">
-        <v>46286.50737268518</v>
-      </c>
-      <c r="D103" t="n">
-        <v>10</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率31，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B104" s="1" t="n">
-        <v>46286.5983912037</v>
-      </c>
-      <c r="C104" s="1" t="n">
-        <v>46286.60533564815</v>
-      </c>
-      <c r="D104" t="n">
-        <v>10</v>
-      </c>
-      <c r="E104" t="inlineStr">
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率21，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>934</v>
+      </c>
+      <c r="B106" s="1" t="n">
+        <v>46289.29210648148</v>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>46289.2990625</v>
+      </c>
+      <c r="D106" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="E106" t="inlineStr">
         <is>
           <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B105" s="1" t="n">
-        <v>46287.11172453704</v>
-      </c>
-      <c r="C105" s="1" t="n">
-        <v>46287.11868055556</v>
-      </c>
-      <c r="D105" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率26，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B106" s="1" t="n">
-        <v>46287.12581018519</v>
-      </c>
-      <c r="C106" s="1" t="n">
-        <v>46287.13274305555</v>
-      </c>
-      <c r="D106" t="n">
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>934</v>
+      </c>
+      <c r="B107" s="1" t="n">
+        <v>46289.30592592592</v>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>46289.31285879629</v>
+      </c>
+      <c r="D107" t="n">
         <v>9.98</v>
       </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率28，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B107" s="1" t="n">
-        <v>46287.30594907407</v>
-      </c>
-      <c r="C107" s="1" t="n">
-        <v>46287.31291666667</v>
-      </c>
-      <c r="D107" t="n">
-        <v>10.03</v>
-      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -3017,17 +3003,17 @@
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>46287.32052083333</v>
+        <v>46286.48706018519</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46287.32746527778</v>
+        <v>46286.49402777778</v>
       </c>
       <c r="D108" t="n">
-        <v>10</v>
+        <v>10.03</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率23，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3043,17 +3029,17 @@
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>46287.38972222222</v>
+        <v>46286.50042824074</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46287.39673611111</v>
+        <v>46286.50737268518</v>
       </c>
       <c r="D109" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率27，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率31，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -3069,17 +3055,17 @@
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>46287.40336805556</v>
+        <v>46286.5983912037</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46287.41027777778</v>
+        <v>46286.60533564815</v>
       </c>
       <c r="D110" t="n">
-        <v>9.949999999999999</v>
+        <v>10</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -3095,17 +3081,17 @@
         </is>
       </c>
       <c r="B111" s="1" t="n">
-        <v>46287.41793981481</v>
+        <v>46287.11172453704</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46287.42490740741</v>
+        <v>46287.11868055556</v>
       </c>
       <c r="D111" t="n">
-        <v>10.03</v>
+        <v>10.02</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率21，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率26，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -3121,17 +3107,17 @@
         </is>
       </c>
       <c r="B112" s="1" t="n">
-        <v>46289.11177083333</v>
+        <v>46287.12581018519</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46289.11864583333</v>
+        <v>46287.13274305555</v>
       </c>
       <c r="D112" t="n">
-        <v>9.9</v>
+        <v>9.98</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率28，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -3147,17 +3133,17 @@
         </is>
       </c>
       <c r="B113" s="1" t="n">
-        <v>46289.1255787037</v>
+        <v>46287.30594907407</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46289.1325</v>
+        <v>46287.31291666667</v>
       </c>
       <c r="D113" t="n">
-        <v>9.970000000000001</v>
+        <v>10.03</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率21，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -3173,17 +3159,17 @@
         </is>
       </c>
       <c r="B114" s="1" t="n">
-        <v>46289.29210648148</v>
+        <v>46287.32052083333</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>46289.2990625</v>
+        <v>46287.32746527778</v>
       </c>
       <c r="D114" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -3199,20 +3185,176 @@
         </is>
       </c>
       <c r="B115" s="1" t="n">
+        <v>46287.38972222222</v>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>46287.39673611111</v>
+      </c>
+      <c r="D115" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率27，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B116" s="1" t="n">
+        <v>46287.40336805556</v>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>46287.41027777778</v>
+      </c>
+      <c r="D116" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="n">
+        <v>46287.41793981481</v>
+      </c>
+      <c r="C117" s="1" t="n">
+        <v>46287.42490740741</v>
+      </c>
+      <c r="D117" t="n">
+        <v>10.03</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率21，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B118" s="1" t="n">
+        <v>46289.11177083333</v>
+      </c>
+      <c r="C118" s="1" t="n">
+        <v>46289.11864583333</v>
+      </c>
+      <c r="D118" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B119" s="1" t="n">
+        <v>46289.1255787037</v>
+      </c>
+      <c r="C119" s="1" t="n">
+        <v>46289.1325</v>
+      </c>
+      <c r="D119" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率21，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B120" s="1" t="n">
+        <v>46289.29210648148</v>
+      </c>
+      <c r="C120" s="1" t="n">
+        <v>46289.2990625</v>
+      </c>
+      <c r="D120" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B121" s="1" t="n">
         <v>46289.30592592592</v>
       </c>
-      <c r="C115" s="1" t="n">
+      <c r="C121" s="1" t="n">
         <v>46289.31285879629</v>
       </c>
-      <c r="D115" t="n">
+      <c r="D121" t="n">
         <v>9.98</v>
       </c>
-      <c r="E115" t="inlineStr">
+      <c r="E121" t="inlineStr">
         <is>
           <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F121" t="inlineStr">
         <is>
           <t>【美团】站点934恢复上线。</t>
         </is>

--- a/data/美团.xlsx
+++ b/data/美团.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3003,17 +3003,17 @@
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>46286.48706018519</v>
+        <v>46286.5983912037</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46286.49402777778</v>
+        <v>46286.60533564815</v>
       </c>
       <c r="D108" t="n">
-        <v>10.03</v>
+        <v>10</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率23，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3029,17 +3029,17 @@
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>46286.50042824074</v>
+        <v>46287.11172453704</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46286.50737268518</v>
+        <v>46287.11868055556</v>
       </c>
       <c r="D109" t="n">
-        <v>10</v>
+        <v>10.02</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率31，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率26，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -3055,17 +3055,17 @@
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>46286.5983912037</v>
+        <v>46287.12581018519</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46286.60533564815</v>
+        <v>46287.13274305555</v>
       </c>
       <c r="D110" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率28，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -3081,17 +3081,17 @@
         </is>
       </c>
       <c r="B111" s="1" t="n">
-        <v>46287.11172453704</v>
+        <v>46287.30594907407</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46287.11868055556</v>
+        <v>46287.31291666667</v>
       </c>
       <c r="D111" t="n">
-        <v>10.02</v>
+        <v>10.03</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率26，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -3107,17 +3107,17 @@
         </is>
       </c>
       <c r="B112" s="1" t="n">
-        <v>46287.12581018519</v>
+        <v>46287.32052083333</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46287.13274305555</v>
+        <v>46287.32746527778</v>
       </c>
       <c r="D112" t="n">
-        <v>9.98</v>
+        <v>10</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率28，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -3133,17 +3133,17 @@
         </is>
       </c>
       <c r="B113" s="1" t="n">
-        <v>46287.30594907407</v>
+        <v>46287.38972222222</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46287.31291666667</v>
+        <v>46287.39673611111</v>
       </c>
       <c r="D113" t="n">
-        <v>10.03</v>
+        <v>10.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率27，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -3159,13 +3159,13 @@
         </is>
       </c>
       <c r="B114" s="1" t="n">
-        <v>46287.32052083333</v>
+        <v>46287.40336805556</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>46287.32746527778</v>
+        <v>46287.41027777778</v>
       </c>
       <c r="D114" t="n">
-        <v>10</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3185,17 +3185,17 @@
         </is>
       </c>
       <c r="B115" s="1" t="n">
-        <v>46287.38972222222</v>
+        <v>46287.41793981481</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46287.39673611111</v>
+        <v>46287.42490740741</v>
       </c>
       <c r="D115" t="n">
-        <v>10.1</v>
+        <v>10.03</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率27，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率21，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -3211,17 +3211,17 @@
         </is>
       </c>
       <c r="B116" s="1" t="n">
-        <v>46287.40336805556</v>
+        <v>46289.11177083333</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>46287.41027777778</v>
+        <v>46289.11864583333</v>
       </c>
       <c r="D116" t="n">
-        <v>9.949999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -3237,13 +3237,13 @@
         </is>
       </c>
       <c r="B117" s="1" t="n">
-        <v>46287.41793981481</v>
+        <v>46289.1255787037</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>46287.42490740741</v>
+        <v>46289.1325</v>
       </c>
       <c r="D117" t="n">
-        <v>10.03</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -3263,17 +3263,17 @@
         </is>
       </c>
       <c r="B118" s="1" t="n">
-        <v>46289.11177083333</v>
+        <v>46289.29210648148</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>46289.11864583333</v>
+        <v>46289.2990625</v>
       </c>
       <c r="D118" t="n">
-        <v>9.9</v>
+        <v>10.02</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -3289,72 +3289,20 @@
         </is>
       </c>
       <c r="B119" s="1" t="n">
-        <v>46289.1255787037</v>
+        <v>46289.30592592592</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>46289.1325</v>
+        <v>46289.31285879629</v>
       </c>
       <c r="D119" t="n">
-        <v>9.970000000000001</v>
+        <v>9.98</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率21，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B120" s="1" t="n">
-        <v>46289.29210648148</v>
-      </c>
-      <c r="C120" s="1" t="n">
-        <v>46289.2990625</v>
-      </c>
-      <c r="D120" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B121" s="1" t="n">
-        <v>46289.30592592592</v>
-      </c>
-      <c r="C121" s="1" t="n">
-        <v>46289.31285879629</v>
-      </c>
-      <c r="D121" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
         <is>
           <t>【美团】站点934恢复上线。</t>
         </is>

--- a/data/美团.xlsx
+++ b/data/美团.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3003,17 +3003,17 @@
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>46286.5983912037</v>
+        <v>46287.38972222222</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46286.60533564815</v>
+        <v>46287.39673611111</v>
       </c>
       <c r="D108" t="n">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率27，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3029,17 +3029,17 @@
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>46287.11172453704</v>
+        <v>46287.40336805556</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46287.11868055556</v>
+        <v>46287.41027777778</v>
       </c>
       <c r="D109" t="n">
-        <v>10.02</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率26，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -3055,17 +3055,17 @@
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>46287.12581018519</v>
+        <v>46287.41793981481</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46287.13274305555</v>
+        <v>46287.42490740741</v>
       </c>
       <c r="D110" t="n">
-        <v>9.98</v>
+        <v>10.03</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率28，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率21，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -3081,17 +3081,17 @@
         </is>
       </c>
       <c r="B111" s="1" t="n">
-        <v>46287.30594907407</v>
+        <v>46289.11177083333</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46287.31291666667</v>
+        <v>46289.11864583333</v>
       </c>
       <c r="D111" t="n">
-        <v>10.03</v>
+        <v>9.9</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -3107,17 +3107,17 @@
         </is>
       </c>
       <c r="B112" s="1" t="n">
-        <v>46287.32052083333</v>
+        <v>46289.1255787037</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46287.32746527778</v>
+        <v>46289.1325</v>
       </c>
       <c r="D112" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率21，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -3133,17 +3133,17 @@
         </is>
       </c>
       <c r="B113" s="1" t="n">
-        <v>46287.38972222222</v>
+        <v>46289.29210648148</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46287.39673611111</v>
+        <v>46289.2990625</v>
       </c>
       <c r="D113" t="n">
-        <v>10.1</v>
+        <v>10.02</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率27，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -3159,13 +3159,13 @@
         </is>
       </c>
       <c r="B114" s="1" t="n">
-        <v>46287.40336805556</v>
+        <v>46289.30592592592</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>46287.41027777778</v>
+        <v>46289.31285879629</v>
       </c>
       <c r="D114" t="n">
-        <v>9.949999999999999</v>
+        <v>9.98</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -3173,136 +3173,6 @@
         </is>
       </c>
       <c r="F114" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B115" s="1" t="n">
-        <v>46287.41793981481</v>
-      </c>
-      <c r="C115" s="1" t="n">
-        <v>46287.42490740741</v>
-      </c>
-      <c r="D115" t="n">
-        <v>10.03</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率21，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B116" s="1" t="n">
-        <v>46289.11177083333</v>
-      </c>
-      <c r="C116" s="1" t="n">
-        <v>46289.11864583333</v>
-      </c>
-      <c r="D116" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B117" s="1" t="n">
-        <v>46289.1255787037</v>
-      </c>
-      <c r="C117" s="1" t="n">
-        <v>46289.1325</v>
-      </c>
-      <c r="D117" t="n">
-        <v>9.970000000000001</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率21，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B118" s="1" t="n">
-        <v>46289.29210648148</v>
-      </c>
-      <c r="C118" s="1" t="n">
-        <v>46289.2990625</v>
-      </c>
-      <c r="D118" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B119" s="1" t="n">
-        <v>46289.30592592592</v>
-      </c>
-      <c r="C119" s="1" t="n">
-        <v>46289.31285879629</v>
-      </c>
-      <c r="D119" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
         <is>
           <t>【美团】站点934恢复上线。</t>
         </is>

--- a/data/美团.xlsx
+++ b/data/美团.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3003,17 +3003,17 @@
         </is>
       </c>
       <c r="B108" s="1" t="n">
-        <v>46287.38972222222</v>
+        <v>46300.40321759259</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>46287.39673611111</v>
+        <v>46300.41016203703</v>
       </c>
       <c r="D108" t="n">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率27，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -3029,17 +3029,17 @@
         </is>
       </c>
       <c r="B109" s="1" t="n">
-        <v>46287.40336805556</v>
+        <v>46300.41730324074</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>46287.41027777778</v>
+        <v>46300.42444444444</v>
       </c>
       <c r="D109" t="n">
-        <v>9.949999999999999</v>
+        <v>10.28</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率22，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -3055,17 +3055,17 @@
         </is>
       </c>
       <c r="B110" s="1" t="n">
-        <v>46287.41793981481</v>
+        <v>46300.43822916667</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>46287.42490740741</v>
+        <v>46300.44517361111</v>
       </c>
       <c r="D110" t="n">
-        <v>10.03</v>
+        <v>10</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率21，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -3081,17 +3081,17 @@
         </is>
       </c>
       <c r="B111" s="1" t="n">
-        <v>46289.11177083333</v>
+        <v>46303.56336805555</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>46289.11864583333</v>
+        <v>46303.57025462963</v>
       </c>
       <c r="D111" t="n">
-        <v>9.9</v>
+        <v>9.92</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率18，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率51，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -3107,72 +3107,20 @@
         </is>
       </c>
       <c r="B112" s="1" t="n">
-        <v>46289.1255787037</v>
+        <v>46303.57733796296</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>46289.1325</v>
+        <v>46303.58429398148</v>
       </c>
       <c r="D112" t="n">
-        <v>9.970000000000001</v>
+        <v>10.02</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率21，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率35，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B113" s="1" t="n">
-        <v>46289.29210648148</v>
-      </c>
-      <c r="C113" s="1" t="n">
-        <v>46289.2990625</v>
-      </c>
-      <c r="D113" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>46289.30592592592</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>46289.31285879629</v>
-      </c>
-      <c r="D114" t="n">
-        <v>9.98</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率20，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
         <is>
           <t>【美团】站点934恢复上线。</t>
         </is>

--- a/data/美团.xlsx
+++ b/data/美团.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2997,10 +2997,8 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
+      <c r="A108" t="n">
+        <v>934</v>
       </c>
       <c r="B108" s="1" t="n">
         <v>46300.40321759259</v>
@@ -3023,10 +3021,8 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
+      <c r="A109" t="n">
+        <v>934</v>
       </c>
       <c r="B109" s="1" t="n">
         <v>46300.41730324074</v>
@@ -3049,10 +3045,8 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
+      <c r="A110" t="n">
+        <v>934</v>
       </c>
       <c r="B110" s="1" t="n">
         <v>46300.43822916667</v>
@@ -3075,10 +3069,8 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
+      <c r="A111" t="n">
+        <v>934</v>
       </c>
       <c r="B111" s="1" t="n">
         <v>46303.56336805555</v>
@@ -3101,10 +3093,8 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
+      <c r="A112" t="n">
+        <v>934</v>
       </c>
       <c r="B112" s="1" t="n">
         <v>46303.57733796296</v>
@@ -3121,6 +3111,136 @@
         </is>
       </c>
       <c r="F112" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B113" s="1" t="n">
+        <v>46300.40321759259</v>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>46300.41016203703</v>
+      </c>
+      <c r="D113" t="n">
+        <v>10</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B114" s="1" t="n">
+        <v>46300.41730324074</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46300.42444444444</v>
+      </c>
+      <c r="D114" t="n">
+        <v>10.28</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率22，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B115" s="1" t="n">
+        <v>46300.43822916667</v>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>46300.44517361111</v>
+      </c>
+      <c r="D115" t="n">
+        <v>10</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B116" s="1" t="n">
+        <v>46303.56336805555</v>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>46303.57025462963</v>
+      </c>
+      <c r="D116" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率51，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B117" s="1" t="n">
+        <v>46303.57733796296</v>
+      </c>
+      <c r="C117" s="1" t="n">
+        <v>46303.58429398148</v>
+      </c>
+      <c r="D117" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率35，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
         <is>
           <t>【美团】站点934恢复上线。</t>
         </is>

--- a/data/美团.xlsx
+++ b/data/美团.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3117,49 +3117,45 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
+      <c r="A113" t="n">
+        <v>934</v>
       </c>
       <c r="B113" s="1" t="n">
-        <v>46300.40321759259</v>
+        <v>46304.67438657407</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>46300.41016203703</v>
+        <v>46304.68136574074</v>
       </c>
       <c r="D113" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率19，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>934</v>
+      </c>
+      <c r="B114" s="1" t="n">
+        <v>46304.68862268519</v>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>46304.69556712963</v>
+      </c>
+      <c r="D114" t="n">
         <v>10</v>
       </c>
-      <c r="E113" t="inlineStr">
+      <c r="E114" t="inlineStr">
         <is>
           <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B114" s="1" t="n">
-        <v>46300.41730324074</v>
-      </c>
-      <c r="C114" s="1" t="n">
-        <v>46300.42444444444</v>
-      </c>
-      <c r="D114" t="n">
-        <v>10.28</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率22，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -3175,17 +3171,17 @@
         </is>
       </c>
       <c r="B115" s="1" t="n">
-        <v>46300.43822916667</v>
+        <v>46300.40321759259</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46300.44517361111</v>
+        <v>46300.41016203703</v>
       </c>
       <c r="D115" t="n">
         <v>10</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -3201,17 +3197,17 @@
         </is>
       </c>
       <c r="B116" s="1" t="n">
-        <v>46303.56336805555</v>
+        <v>46300.41730324074</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>46303.57025462963</v>
+        <v>46300.42444444444</v>
       </c>
       <c r="D116" t="n">
-        <v>9.92</v>
+        <v>10.28</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率51，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率22，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -3227,20 +3223,124 @@
         </is>
       </c>
       <c r="B117" s="1" t="n">
+        <v>46300.43822916667</v>
+      </c>
+      <c r="C117" s="1" t="n">
+        <v>46300.44517361111</v>
+      </c>
+      <c r="D117" t="n">
+        <v>10</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B118" s="1" t="n">
+        <v>46303.56336805555</v>
+      </c>
+      <c r="C118" s="1" t="n">
+        <v>46303.57025462963</v>
+      </c>
+      <c r="D118" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率51，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B119" s="1" t="n">
         <v>46303.57733796296</v>
       </c>
-      <c r="C117" s="1" t="n">
+      <c r="C119" s="1" t="n">
         <v>46303.58429398148</v>
       </c>
-      <c r="D117" t="n">
+      <c r="D119" t="n">
         <v>10.02</v>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E119" t="inlineStr">
         <is>
           <t>【美团】站点934：预定验价变价率35，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B120" s="1" t="n">
+        <v>46304.67438657407</v>
+      </c>
+      <c r="C120" s="1" t="n">
+        <v>46304.68136574074</v>
+      </c>
+      <c r="D120" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率19，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>【美团】站点934恢复上线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="B121" s="1" t="n">
+        <v>46304.68862268519</v>
+      </c>
+      <c r="C121" s="1" t="n">
+        <v>46304.69556712963</v>
+      </c>
+      <c r="D121" t="n">
+        <v>10</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
         <is>
           <t>【美团】站点934恢复上线。</t>
         </is>

--- a/data/美团.xlsx
+++ b/data/美团.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3171,17 +3171,17 @@
         </is>
       </c>
       <c r="B115" s="1" t="n">
-        <v>46300.40321759259</v>
+        <v>46303.56336805555</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46300.41016203703</v>
+        <v>46303.57025462963</v>
       </c>
       <c r="D115" t="n">
-        <v>10</v>
+        <v>9.92</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率51，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -3197,17 +3197,17 @@
         </is>
       </c>
       <c r="B116" s="1" t="n">
-        <v>46300.41730324074</v>
+        <v>46303.57733796296</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>46300.42444444444</v>
+        <v>46303.58429398148</v>
       </c>
       <c r="D116" t="n">
-        <v>10.28</v>
+        <v>10.02</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率22，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率35，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -3223,17 +3223,17 @@
         </is>
       </c>
       <c r="B117" s="1" t="n">
-        <v>46300.43822916667</v>
+        <v>46304.67438657407</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>46300.44517361111</v>
+        <v>46304.68136574074</v>
       </c>
       <c r="D117" t="n">
-        <v>10</v>
+        <v>10.05</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率16，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率19，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -3249,98 +3249,20 @@
         </is>
       </c>
       <c r="B118" s="1" t="n">
-        <v>46303.56336805555</v>
+        <v>46304.68862268519</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>46303.57025462963</v>
+        <v>46304.69556712963</v>
       </c>
       <c r="D118" t="n">
-        <v>9.92</v>
+        <v>10</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率51，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B119" s="1" t="n">
-        <v>46303.57733796296</v>
-      </c>
-      <c r="C119" s="1" t="n">
-        <v>46303.58429398148</v>
-      </c>
-      <c r="D119" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率35，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B120" s="1" t="n">
-        <v>46304.67438657407</v>
-      </c>
-      <c r="C120" s="1" t="n">
-        <v>46304.68136574074</v>
-      </c>
-      <c r="D120" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率19，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B121" s="1" t="n">
-        <v>46304.68862268519</v>
-      </c>
-      <c r="C121" s="1" t="n">
-        <v>46304.69556712963</v>
-      </c>
-      <c r="D121" t="n">
-        <v>10</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
         <is>
           <t>【美团】站点934恢复上线。</t>
         </is>

--- a/data/美团.xlsx
+++ b/data/美团.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3171,17 +3171,17 @@
         </is>
       </c>
       <c r="B115" s="1" t="n">
-        <v>46303.56336805555</v>
+        <v>46304.67438657407</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>46303.57025462963</v>
+        <v>46304.68136574074</v>
       </c>
       <c r="D115" t="n">
-        <v>9.92</v>
+        <v>10.05</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率51，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率19，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -3197,72 +3197,20 @@
         </is>
       </c>
       <c r="B116" s="1" t="n">
-        <v>46303.57733796296</v>
+        <v>46304.68862268519</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>46303.58429398148</v>
+        <v>46304.69556712963</v>
       </c>
       <c r="D116" t="n">
-        <v>10.02</v>
+        <v>10</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>【美团】站点934：预定验价变价率35，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
+          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B117" s="1" t="n">
-        <v>46304.67438657407</v>
-      </c>
-      <c r="C117" s="1" t="n">
-        <v>46304.68136574074</v>
-      </c>
-      <c r="D117" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率19，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>【美团】站点934恢复上线。</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>934</t>
-        </is>
-      </c>
-      <c r="B118" s="1" t="n">
-        <v>46304.68862268519</v>
-      </c>
-      <c r="C118" s="1" t="n">
-        <v>46304.69556712963</v>
-      </c>
-      <c r="D118" t="n">
-        <v>10</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>【美团】站点934：预定验价变价率17，下线，请及时处理。具体原因及日志请查看「美团机票商家端系统-合作商监控-预定记录」</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
         <is>
           <t>【美团】站点934恢复上线。</t>
         </is>
